--- a/foundational_documents/DOT_signal_overview.xlsx
+++ b/foundational_documents/DOT_signal_overview.xlsx
@@ -47,7 +47,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +84,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8DAEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -111,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -135,6 +140,8 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3289,6 +3296,135 @@
       </c>
       <c r="M59" s="4" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE-VARIABLE (S.20) — conviction sizing + gap entries</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="n"/>
+      <c r="C61" s="15" t="n"/>
+      <c r="D61" s="15" t="n"/>
+      <c r="E61" s="15" t="n"/>
+      <c r="F61" s="15" t="n"/>
+      <c r="G61" s="15" t="n"/>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="15" t="n"/>
+      <c r="J61" s="15" t="n"/>
+      <c r="K61" s="15" t="n"/>
+      <c r="L61" s="15" t="n"/>
+      <c r="M61" s="15" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>SV_Hurst_L</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>6090.6</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>19/20</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>-118</v>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>SV_FailBrk_L</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>19834.1</v>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>22/22</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3312,7 +3448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5787,6 +5923,108 @@
       <c r="F83" s="4" t="inlineStr">
         <is>
           <t>discrete state/side == value</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>S.20 CONVICTION / GAP THRESHOLDS</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="n"/>
+      <c r="C85" s="15" t="n"/>
+      <c r="D85" s="15" t="n"/>
+      <c r="E85" s="15" t="n"/>
+      <c r="F85" s="15" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Micro_Hurst</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>p90</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>ADAPTIVE (rolling-2500)</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>conviction SIZING gate: book longs &gt; p90 -&gt; 2.0 lots (longs only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Micro_Hurst</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>p97</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>ADAPTIVE (rolling-2500)</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Hurst GAP-single: &gt; p97 &amp; D2D+ -&gt; LONG 1 lot LOCK=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Micro_FailedBreak</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>p90</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>ADAPTIVE (rolling-2500)</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>FailedBreak GAP-single: &gt; p90 &amp; D2D- (reversion) -&gt; LONG 1 lot LOCK=3; recentFB sizing x1.25</t>
         </is>
       </c>
     </row>
@@ -5805,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6145,6 +6383,39 @@
       <c r="I9" s="6" t="n">
         <v>0.009430715219935293</v>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>SINGLE-VARIABLE (S.20)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Lone-variable conviction: Micro_Hurst trend-persistence + Micro_FailedBreak reversion — sizes book longs and fills gaps (addendum to the 8 structures)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>467</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>25925</v>
+      </c>
+      <c r="I10" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/foundational_documents/DOT_signal_overview.xlsx
+++ b/foundational_documents/DOT_signal_overview.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Threshold Tiers" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Read This" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D2D" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,8 +48,14 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +97,11 @@
         <fgColor rgb="00E8DAEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -142,6 +155,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3427,13 +3448,182 @@
         <v>2</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>D2D_BREAK_OF_STRUCTURE (9th) — Adaptive break-of-structure / directional-flip regime; the founding OBVf engine (standalone 32 tr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>D0</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>D2D_Throne</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>D2D-flip</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F65" s="22" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="G65" s="23" t="n">
+        <v>16.89</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>D2D_Throne_L</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>D2D-flip</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F66" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="23" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>DS</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>D2D_Throne_S</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>D2D-flip</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="F67" s="22" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="G67" s="23" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>D2D_Conviction</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>sizer</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>D2D_Gap</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>D2D-gap</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="F69" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="23" t="n">
+        <v>999</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A58:M58"/>
     <mergeCell ref="A40:M40"/>
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="A56:M56"/>
     <mergeCell ref="A51:M51"/>
+    <mergeCell ref="A64:G64"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A33:M33"/>
     <mergeCell ref="A49:M49"/>
@@ -3448,7 +3638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6028,9 +6218,77 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>S.21 D2D CROWN-JEWEL THRESHOLDS (throne gate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>Micro_Hurst</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>p30</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t>ADAPTIVE (rolling-2500)</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="inlineStr">
+        <is>
+          <t>D2D throne gate: Hurst&gt;=p30 &amp; ADX&gt;=30 &amp; D2D-flip -&gt; conviction 2x (both dir) + gap-filler flat-2-lot</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>ADX_Value</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>&gt;=30</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>D2D throne trend-strength floor for the conviction sizer + gap-filler</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A90:F90"/>
     <mergeCell ref="A62:F62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6534,4 +6792,379 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>D2D — THE FOUNDING SYSTEM (adaptive break-of-structure / directional-flip engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Anthony's original custom-OBVf-driven directional system, live in equiDOT.cs; ratified TM (native SuperTrend trail FORBIDDEN). The 9th market structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>STANDALONE THRONE SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>32 (18L / 14S)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>both directions</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Win Rate</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>96.9%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>one loss in ~5 months (a single -$153 SL, in March)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net P&amp;L $</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2,431</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1-lot base, true $1/pt (STANDALONE — separate from the $92,347 combined system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Worst Day $</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-153.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>inside the FTMO -$2,500 daily gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Max Drawdown $</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-153.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Folds positive / min-fold PF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6/6 / 1.72</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>March holds the lone loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OOS (May-Jun)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>n12, 100% WR, PF 999, net $1,111</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>no OOS losers</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Exit mix</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SL 1 (-153) / BE 25 (850) / LF 6 (1,734)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>the runner (LF) carries the net</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Per-fold PF</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jan 999 / Feb 999 / Mar 1.72 / Apr 999 / May 999 / Jun 999</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>LONG / SHORT RULES (separate standalone configs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>WR% / PF</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>Net $ / Worst Day / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D2D LONG-only</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>100.0% / 999</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>$1,651 / +20 / NO losing day (max-DD 0.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D2D SHORT-only</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>92.9% / 6.10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>$780 / -153 / the lone system loss is here (March)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>ROLES IN THE COMBINED SYSTEM (S.21 crown jewel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C1 D2D-Conviction</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2x sizer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>D2D_Signal==dir &amp; ADX&gt;=30 &amp; Micro_Hurst&gt;=p30 -&gt; up-size a book trade 2x (higher-mult-wins, never 4x); the ONLY short conviction source</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G1 D2D-Gap-Filler</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>flat-2-lot</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>throne entry fired when zero Dots open -&gt; flat 2.0 lots, bypasses conviction (no 4x); 14 trades (4L/10S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Crown-jewel contribution: Role 2 conviction +$1,015 + Role 1 gap +$1,900 -&gt; combined DOT+D2D system $92,347 (verified DIRECTLY, not summed). This tab records the STANDALONE object; $92,347 is the combined-system canonical.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/foundational_documents/DOT_signal_overview.xlsx
+++ b/foundational_documents/DOT_signal_overview.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,7 @@
     <font>
       <i val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="10">
     <fill>
@@ -129,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -163,6 +164,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6800,7 +6802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7153,6 +7155,34 @@
       <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Crown-jewel contribution: Role 2 conviction +$1,015 + Role 1 gap +$1,900 -&gt; combined DOT+D2D system $92,347 (verified DIRECTLY, not summed). This tab records the STANDALONE object; $92,347 is the combined-system canonical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>!! 2026-07-27 EXPORT-CLOCK NOTE — EVERY FIGURE ON THIS SHEET WAS MEASURED WITH FRIDAY AFTERNOONS EXCLUDED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>DOT.cs L730-731 exported a clock 2-3h fast (the bar's SERVER time was fed into a parameter declared gmtTime), so portfolio_simulation_engine.py L148's Friday gate fired from true 13:00 EST instead of 16:45 and removed roughly the last three hours of every Friday cash session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Corrected-clock re-score of the same sealed-baseline window: 2,739 tr / WR 91.9% / PF 5.92 / net $91,506 (+41 tr, -$789 vs the $92,296 the recorded $92,347 reproduces at on the broken clock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>THE FIGURES ON THIS SHEET STAND AS THE HISTORICAL RECORD — they are NOT corrected-clock numbers. The LIVE EA clock was always correct. Law: S.22 non_negotiables_developer.txt. Detail: DOT_codebase_map.md section 5.</t>
         </is>
       </c>
     </row>
